--- a/tools/importer/reports/import-home-page.report.xlsx
+++ b/tools/importer/reports/import-home-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>home-page</t>
   </si>
   <si>
-    <t>2026-08-21T19:10:13.968Z</t>
+    <t>2026-08-22T22:59:39.287Z</t>
   </si>
   <si>
     <t>Home</t>

--- a/tools/importer/reports/import-home-page.report.xlsx
+++ b/tools/importer/reports/import-home-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>home-page</t>
   </si>
   <si>
-    <t>2026-08-22T22:59:39.287Z</t>
+    <t>2026-09-05T00:19:34.517Z</t>
   </si>
   <si>
     <t>Home</t>

--- a/tools/importer/reports/import-home-page.report.xlsx
+++ b/tools/importer/reports/import-home-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>home-page</t>
   </si>
   <si>
-    <t>2026-09-05T00:19:34.517Z</t>
+    <t>2026-09-05T11:14:08.278Z</t>
   </si>
   <si>
     <t>Home</t>
